--- a/assessment_forms/028_phone_vocabulary_assessment--assessment_forms.xlsx
+++ b/assessment_forms/028_phone_vocabulary_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>phone_vocabulary_assessment_helps_educators_and_trainers_evaluate_telecom_terminology_knowledge_online_with_jotform_supporting_fast_data_collection_and_easy_review_of_each_form_submission</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Understanding of PBX</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Assess the participant's understanding of PBX and its role in telecom networks</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,12 +547,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question1</t>
+          <t>pbx_question1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_a_pbx</t>
+          <t>What is PBX</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +570,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question2</t>
+          <t>cell_network_question1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_is_a_bts</t>
+          <t>What is a cellular network?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +588,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question3</t>
+          <t>telecom_exchange_question1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_is_a_cellular_network</t>
+          <t>What is telecom exchange?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +611,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question4</t>
+          <t>switching_systems_question1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_is_a_telecom_switch</t>
+          <t>What are switching systems?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +639,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question5</t>
+          <t>site_management_question1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_is_a_telecom_exchange</t>
+          <t>How is a cell site managed?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +662,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question6</t>
+          <t>troubleshooting_question1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_is_a_telecom_switching_system</t>
+          <t>Describe a method for troubleshooting a telecom issue</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +685,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question7</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what_is_a_bts_switch</t>
+          <t>Additional information</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +708,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question8</t>
+          <t>site_optimization_question1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what_is_a_cell_site</t>
+          <t>How do you optimize a cell site?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +731,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question9</t>
+          <t>network_optimization_question1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>what_is_a_bts_site</t>
+          <t>How do you optimize a telecom network?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +754,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question10</t>
+          <t>network_management_question1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>what_is_a_bts_switch</t>
+          <t>How is a telecom network managed?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question11</t>
+          <t>exchange_management_question1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>what_is_a_cell_site</t>
+          <t>How is a telecom exchange managed?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +800,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question12</t>
+          <t>exchange_optimization_question1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>what_is_a_pbx_switch</t>
+          <t>How do you optimize a telecom exchange?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +823,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question13</t>
+          <t>pbx_management_question1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>what_is_a_telecom_exchange</t>
+          <t>How is PBX managed?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question15</t>
+          <t>network_security_question1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>what_is_a_bts</t>
+          <t>What measures are taken to secure a telecom network?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question16</t>
+          <t>site_security_question1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>what_is_a_cell_site</t>
+          <t>What measures are taken to secure a cell site?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question17</t>
+          <t>network_analysis_question1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>what_is_a_bts_switch</t>
+          <t>How is a telecom network analyzed?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +915,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question18</t>
+          <t>final_question</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>what_is_a_cell_network</t>
+          <t>Final question</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>what_is_a_pbx</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>what_is_a_telecom_network</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>what_is_a_telecom_switch</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>what_is_a_telecom_exchange</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>what_is_a_bts_site</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>what_is_a_cell_site</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>what_is_a_bts</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +941,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,153 +969,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>pbx_question1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>private_branch_exchange_(pbx)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Private Branch Exchange (PBX)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>pbx_question1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>public_branch_exchange_(pbx)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Public Branch eXchange (PBX)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question1_choices</t>
+          <t>pbx_question1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>phone_branch_system_(pbx)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Phone Branch System (PBX)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>cell_network_question1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>a_network_of_cell_phones</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>A network of cell phones</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>cell_network_question1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>a_network_of_cell_towers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>A network of cell towers</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>cell_network_question1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>a_network_of_cellular_communication_systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>A network of cellular communication systems</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question3_choices</t>
+          <t>telecom_exchange_question1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>a_place_where_multiple_networks_meet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>A place where multiple networks meet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question3_choices</t>
+          <t>telecom_exchange_question1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>a_platform_for_inter-network_communication</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>A platform for inter-network communication</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question3_choices</t>
+          <t>telecom_exchange_question1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>a_device_for_switching_between_networks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>A device for switching between networks</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>switching_systems_question1_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>pbx_systems</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PBX systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>switching_systems_question1_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bts_systems</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BTS systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>switching_systems_question1_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cellular_switching_systems</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cellular switching systems</t>
         </is>
       </c>
     </row>
